--- a/data/trans_dic/P21D_3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_3_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,91</t>
+          <t>0,08; 0,93</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 0,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,37</t>
+          <t>0,03; 0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,21</t>
+          <t>0,02; 0,22</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1776</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1328</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1527</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1270</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1492</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4193</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1165</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2973</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1765</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3835</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3485</t>
+          <t>0; 3983</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4665</t>
+          <t>0; 4590</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>541; 5831</t>
+          <t>539; 5949</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4140</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1259</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1566</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4508</t>
+          <t>0; 3682</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>541; 5686</t>
+          <t>540; 5904</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>708; 6589</t>
+          <t>746; 7072</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21D_3_R-Clase-trans_dic.xlsx
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,5</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,93</t>
+          <t>0,08; 0,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,23</t>
+          <t>0,0; 0,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,38</t>
+          <t>0,03; 0,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,22</t>
+          <t>0,02; 0,21</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>0; 4393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3983</t>
+          <t>0; 3525</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2057</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3625</t>
+          <t>0; 4455</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4590</t>
+          <t>0; 4713</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>539; 5949</t>
+          <t>555; 5193</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3682</t>
+          <t>0; 3973</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>540; 5904</t>
+          <t>567; 5631</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>746; 7072</t>
+          <t>708; 6630</t>
         </is>
       </c>
     </row>
